--- a/Shallap/Parameters/Site_Config_TC.xlsx
+++ b/Shallap/Parameters/Site_Config_TC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\group\pelligrp\Project_folders\MountainWater\Tethys_Chloris\Workflow_dev\Scripts\Cat\TeC_Source_Code\Shallap\Parameters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B038346-61E9-4FDC-A6E0-66232E666D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A16A0C1-7DC7-447A-B889-B9434468C905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-5475" windowWidth="29040" windowHeight="17520" xr2:uid="{88CAB792-6FF5-4371-9CFE-4BFDB664029A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>Variable</t>
   </si>
@@ -147,18 +147,6 @@
     <t>Meteo_el</t>
   </si>
   <si>
-    <t>SM_Data_cl_and_fl_20260202.mat</t>
-  </si>
-  <si>
-    <t>SM_fl4_hourly</t>
-  </si>
-  <si>
-    <t>SH_hm_Ta_lapse.mat</t>
-  </si>
-  <si>
-    <t>SH_hm_lapse</t>
-  </si>
-  <si>
     <t>File name of meteorological station (used if OPT_Forcing = 1) (.mat)</t>
   </si>
   <si>
@@ -214,6 +202,30 @@
   </si>
   <si>
     <t xml:space="preserve">Choose if vegetation parameters (for Ccrown, Cwat, Crock, Curb, Cbare) are one value per landcover type (1), or gridded and variable per landcover (2). For 1 change the values in VPAR_T directly, for 2 provide the grids in the dtm_file.  Note for 2 you still need the table to read the Veg_type names but the values are not used. </t>
+  </si>
+  <si>
+    <t>Meteo_data_short</t>
+  </si>
+  <si>
+    <t>SM_Data_cl_and_fl_20260202_tidy.mat</t>
+  </si>
+  <si>
+    <t>SH_hm_Ta_lapse_tidy.mat</t>
+  </si>
+  <si>
+    <t>hm_Ta_lapse</t>
+  </si>
+  <si>
+    <t>t_bef</t>
+  </si>
+  <si>
+    <t>t_aft</t>
+  </si>
+  <si>
+    <t>Integration interval for solar variables – Hours or fractions before (ONLY for OPT_Forcing = 2)</t>
+  </si>
+  <si>
+    <t>Integration interval for solar variables – Hours or fractions after (ONLY for OPT_Forcing = 2)</t>
   </si>
 </sst>
 </file>
@@ -578,7 +590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3599F18B-EE60-4F0C-96C4-516BFFC819B6}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.1796875" customWidth="1"/>
@@ -720,24 +732,24 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
@@ -748,7 +760,7 @@
         <v>4767</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
@@ -756,10 +768,10 @@
         <v>29</v>
       </c>
       <c r="B16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" t="s">
         <v>36</v>
-      </c>
-      <c r="C16" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -767,10 +779,10 @@
         <v>30</v>
       </c>
       <c r="B17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" t="s">
         <v>37</v>
-      </c>
-      <c r="C17" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
@@ -778,10 +790,10 @@
         <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
@@ -789,10 +801,10 @@
         <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="C19" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
@@ -800,10 +812,10 @@
         <v>33</v>
       </c>
       <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
         <v>42</v>
-      </c>
-      <c r="C20" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -811,32 +823,48 @@
         <v>34</v>
       </c>
       <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
         <v>43</v>
-      </c>
-      <c r="C21" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" t="s">
         <v>48</v>
-      </c>
-      <c r="B22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B23" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
